--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487201_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487201_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.9937</v>
+        <v>8.0762</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6072</v>
+        <v>3.3054</v>
       </c>
       <c r="F2" t="n">
-        <v>5.3865</v>
+        <v>4.7708</v>
       </c>
       <c r="G2" t="n">
         <v>3.733</v>
@@ -610,13 +610,13 @@
         <v>1.7371</v>
       </c>
       <c r="S2" t="n">
-        <v>3.882</v>
+        <v>1.9644</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4021</v>
+        <v>1.1002</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4799</v>
+        <v>0.8642</v>
       </c>
       <c r="V2" t="n">
         <v>1.7997</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7162</v>
+        <v>4.8441</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5267</v>
+        <v>2.2263</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1895</v>
+        <v>2.6178</v>
       </c>
       <c r="G3" t="n">
         <v>4.3947</v>
@@ -688,13 +688,13 @@
         <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8183</v>
+        <v>0.9462</v>
       </c>
       <c r="T3" t="n">
-        <v>0.591</v>
+        <v>0.2905</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2274</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>1.4333</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. EGUSKITZA AGINALDE</t>
+          <t>A. OLIVEIRA GETE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4392</v>
+        <v>4.5471</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7228</v>
+        <v>2.1811</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7165</v>
+        <v>2.366</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7141</v>
+        <v>4.338</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4254</v>
+        <v>2.0731</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2888</v>
+        <v>2.2649</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0052</v>
+        <v>2.4349</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0516</v>
+        <v>1.0918</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9536</v>
+        <v>1.3431</v>
       </c>
       <c r="M4" t="n">
-        <v>1.7089</v>
+        <v>1.9031</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3737</v>
+        <v>0.9813</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3352</v>
+        <v>0.9218</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.965</v>
+        <v>0.965</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1231</v>
+        <v>-0.193</v>
       </c>
       <c r="R4" t="n">
         <v>1.158</v>
       </c>
       <c r="S4" t="n">
-        <v>0.585</v>
+        <v>0.5949</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3847</v>
+        <v>-0.0608</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2003</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1052</v>
+        <v>-1.3508</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4559</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>-1.3508</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. OLIVEIRA GETE</t>
+          <t>A. EGUSKITZA AGINALDE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2536</v>
+        <v>4.4263</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7805</v>
+        <v>2.5225</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4731</v>
+        <v>1.9039</v>
       </c>
       <c r="G5" t="n">
-        <v>4.338</v>
+        <v>3.7141</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0731</v>
+        <v>0.4254</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2649</v>
+        <v>3.2888</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4349</v>
+        <v>2.0052</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0918</v>
+        <v>0.0516</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3431</v>
+        <v>1.9536</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9031</v>
+        <v>1.7089</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9813</v>
+        <v>0.3737</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9218</v>
+        <v>1.3352</v>
       </c>
       <c r="P5" t="n">
-        <v>0.965</v>
+        <v>-0.965</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.193</v>
+        <v>-2.1231</v>
       </c>
       <c r="R5" t="n">
         <v>1.158</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3014</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4614</v>
+        <v>0.1844</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7627</v>
+        <v>0.3876</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.3508</v>
+        <v>1.1052</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.4559</v>
       </c>
       <c r="X5" t="n">
         <v>-1.3508</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ZUBIZARRETA ALBIZU</t>
+          <t>A. BOZAL GOMEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5808</v>
+        <v>1.9975</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2909</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.29</v>
+        <v>1.0081</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9175</v>
+        <v>3.1393</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0921</v>
+        <v>1.7212</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8254</v>
+        <v>1.418</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0645</v>
+        <v>1.2432</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3726</v>
+        <v>1.1539</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6919</v>
+        <v>0.0893</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1469</v>
+        <v>1.8961</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2805</v>
+        <v>0.5673</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1335</v>
+        <v>1.3288</v>
       </c>
       <c r="P6" t="n">
-        <v>0.193</v>
+        <v>1.3511</v>
       </c>
       <c r="Q6" t="n">
+        <v>-0.193</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.5441</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.0608</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.4326</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-2.8646</v>
+      </c>
+      <c r="W6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
-        <v>0.193</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.1844</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.0595</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.2439</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.2859</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.2859</v>
-      </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.8646</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BOZAL GOMEZ</t>
+          <t>E. JUARROS CASTAÑO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3025</v>
+        <v>1.889</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5888</v>
+        <v>0.9568</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7137</v>
+        <v>0.9322</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1393</v>
+        <v>0.4507</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7212</v>
+        <v>2.2107</v>
       </c>
       <c r="I7" t="n">
-        <v>1.418</v>
+        <v>-1.7601</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2432</v>
+        <v>1.4052</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1539</v>
+        <v>3.2859</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0893</v>
+        <v>-1.8807</v>
       </c>
       <c r="M7" t="n">
-        <v>1.8961</v>
+        <v>-0.9546</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5673</v>
+        <v>-1.0752</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3288</v>
+        <v>0.1207</v>
       </c>
       <c r="P7" t="n">
         <v>1.3511</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.193</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3232</v>
+        <v>0.4154</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4614</v>
+        <v>-0.1203</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1381</v>
+        <v>0.5357</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.8646</v>
+        <v>-0.3281</v>
       </c>
       <c r="W7" t="n">
+        <v>-0.3281</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-2.8646</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. EGAA AYERZA</t>
+          <t>M. ZUBIZARRETA ALBIZU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2984</v>
+        <v>1.6007</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5034</v>
+        <v>1.391</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.2097</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3798</v>
+        <v>0.9175</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0845</v>
+        <v>0.0921</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7047</v>
+        <v>0.8254</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7019</v>
+        <v>1.0645</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1242</v>
+        <v>0.3726</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5777</v>
+        <v>0.6919</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0817</v>
+        <v>-0.1469</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2087</v>
+        <v>-0.2805</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1271</v>
+        <v>0.1335</v>
       </c>
       <c r="P8" t="n">
-        <v>0.386</v>
+        <v>0.193</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3511</v>
+        <v>0.193</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6782</v>
+        <v>0.2042</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4614</v>
+        <v>0.0407</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1395</v>
+        <v>0.1636</v>
       </c>
       <c r="V8" t="n">
-        <v>0.614</v>
+        <v>0.2859</v>
       </c>
       <c r="W8" t="n">
-        <v>1.228</v>
+        <v>0.2859</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. JUARROS CASTAÑO</t>
+          <t>J. EGAA AYERZA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0869</v>
+        <v>1.3777</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5563</v>
+        <v>0.904</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.4737</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4507</v>
+        <v>-0.3798</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2107</v>
+        <v>-1.0845</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7601</v>
+        <v>0.7047</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4052</v>
+        <v>0.7019</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2859</v>
+        <v>0.1242</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8807</v>
+        <v>0.5777</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9546</v>
+        <v>-1.0817</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0752</v>
+        <v>-1.2087</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1207</v>
+        <v>0.1271</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3511</v>
+        <v>0.386</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R9" t="n">
         <v>1.3511</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3867</v>
+        <v>0.7575</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5208</v>
+        <v>-0.0608</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1342</v>
+        <v>0.8183</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3281</v>
+        <v>0.614</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3281</v>
+        <v>1.228</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7886</v>
+        <v>-0.7618</v>
       </c>
       <c r="E10" t="n">
         <v>-0.1785</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6101</v>
+        <v>-0.5834</v>
       </c>
       <c r="G10" t="n">
         <v>-0.821</v>
@@ -1234,13 +1234,13 @@
         <v>0.193</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1606</v>
+        <v>-0.1338</v>
       </c>
       <c r="T10" t="n">
         <v>-0.1785</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7375</v>
+        <v>-2.1856</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0169</v>
+        <v>-2.117</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2794</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>2.1006</v>
@@ -1312,13 +1312,13 @@
         <v>0.965</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3729</v>
+        <v>0.9247</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0462</v>
+        <v>-0.1464</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4191</v>
+        <v>1.0711</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3508</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1227</v>
+        <v>-3.083</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3978</v>
+        <v>-2.1975</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7249</v>
+        <v>-0.8856000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2783</v>
@@ -1390,13 +1390,13 @@
         <v>0.579</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4138</v>
+        <v>0.4534</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.238</v>
+        <v>-0.0377</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.4911</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9421</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.9578</v>
+        <v>-4.6633</v>
       </c>
       <c r="E13" t="n">
         <v>-4.8951</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.06270000000000001</v>
+        <v>0.2318</v>
       </c>
       <c r="G13" t="n">
         <v>-2.7204</v>
@@ -1468,13 +1468,13 @@
         <v>1.158</v>
       </c>
       <c r="S13" t="n">
-        <v>0.507</v>
+        <v>0.8015</v>
       </c>
       <c r="T13" t="n">
         <v>0.1468</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3602</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-0.0422</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.0647</v>
+        <v>18.0649</v>
       </c>
       <c r="E14" t="n">
-        <v>5.088299999999999</v>
+        <v>5.088400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>12.9766</v>
+        <v>12.9764</v>
       </c>
       <c r="G14" t="n">
         <v>18.5884</v>
@@ -1546,13 +1546,13 @@
         <v>13.5105</v>
       </c>
       <c r="S14" t="n">
-        <v>7.8725</v>
+        <v>7.8723</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0974</v>
+        <v>1.0973</v>
       </c>
       <c r="U14" t="n">
-        <v>6.774800000000001</v>
+        <v>6.7749</v>
       </c>
       <c r="V14" t="n">
         <v>-1.6405</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4434</v>
+        <v>2.7306</v>
       </c>
       <c r="E15" t="n">
-        <v>3.451</v>
+        <v>3.5512</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0076</v>
+        <v>-0.8206</v>
       </c>
       <c r="G15" t="n">
         <v>0.8045</v>
@@ -1624,13 +1624,13 @@
         <v>2.3161</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0629</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8923</v>
+        <v>-0.7922</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1706</v>
+        <v>0.0165</v>
       </c>
       <c r="V15" t="n">
         <v>1.3508</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>I. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9016999999999999</v>
+        <v>0.662</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9859</v>
+        <v>0.2086</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0842</v>
+        <v>0.4534</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.2756</v>
+        <v>0.9821</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.3506</v>
+        <v>-0.5402</v>
       </c>
       <c r="I16" t="n">
-        <v>0.075</v>
+        <v>1.5223</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.1146</v>
+        <v>1.2824</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.7494</v>
+        <v>0.0207</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6348</v>
+        <v>1.2617</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.161</v>
+        <v>-0.3003</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6012</v>
+        <v>-0.5609</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5598</v>
+        <v>0.2606</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5441</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
+        <v>-0.965</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.1973</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.1087</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.0886</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.1228</v>
+      </c>
+      <c r="W16" t="n">
         <v>0</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.5441</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.0596</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.8725000000000001</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.5737</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.228</v>
-      </c>
       <c r="X16" t="n">
-        <v>-0.6543</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. HANSEN GUTIERREZ</t>
+          <t>P. HERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7218</v>
+        <v>0.2323</v>
       </c>
       <c r="E17" t="n">
-        <v>0.509</v>
+        <v>-0.3146</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2128</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9821</v>
+        <v>0.0436</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5402</v>
+        <v>1.211</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5223</v>
+        <v>-1.1674</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2824</v>
+        <v>-0.5907</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0207</v>
+        <v>0.7038</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2617</v>
+        <v>-1.2945</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3003</v>
+        <v>0.6343</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5609</v>
+        <v>0.5072</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2606</v>
+        <v>0.1271</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>1.3511</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1375</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1917</v>
+        <v>-0.9518</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3292</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1228</v>
+        <v>-0.2859</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1228</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ BLANCO</t>
+          <t>E. GUTIERREZ O´CALLAGHAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0083</v>
+        <v>-0.1807</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3146</v>
+        <v>-0.0155</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3063</v>
+        <v>-0.1651</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0436</v>
+        <v>-2.2756</v>
       </c>
       <c r="H18" t="n">
-        <v>1.211</v>
+        <v>-2.3506</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1674</v>
+        <v>0.075</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5907</v>
+        <v>-1.1146</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7038</v>
+        <v>-1.7494</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2945</v>
+        <v>0.6348</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6343</v>
+        <v>-1.161</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5072</v>
+        <v>-0.6012</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1271</v>
+        <v>-0.5598</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1171</v>
+        <v>-0.0228</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9518</v>
+        <v>-0.1289</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1653</v>
+        <v>0.1061</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2859</v>
+        <v>0.5737</v>
       </c>
       <c r="W18" t="n">
         <v>1.228</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.5138</v>
+        <v>-0.6543</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5038</v>
+        <v>-1.4635</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8359</v>
+        <v>-2.0362</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3321</v>
+        <v>0.5727</v>
       </c>
       <c r="G19" t="n">
         <v>-1.3622</v>
@@ -1936,13 +1936,13 @@
         <v>1.158</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5975</v>
+        <v>-0.5572</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1652</v>
+        <v>-0.3655</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4323</v>
+        <v>-0.1917</v>
       </c>
       <c r="V19" t="n">
         <v>1.228</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. MUZQUIZ GURREA</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0026</v>
+        <v>-1.7981</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6279</v>
+        <v>-1.5574</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3746</v>
+        <v>-0.2407</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6178</v>
+        <v>-1.6568</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9717</v>
+        <v>0.2775</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6462</v>
+        <v>-1.9343</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7356</v>
+        <v>-1.1762</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7763</v>
+        <v>0.7452</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0407</v>
+        <v>-1.9214</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8822</v>
+        <v>-0.4805</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1953</v>
+        <v>-0.4677</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6869</v>
+        <v>-0.0129</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5091</v>
+        <v>0.579</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5091</v>
+        <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2994</v>
+        <v>-0.8834</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8923</v>
+        <v>-0.93</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5929</v>
+        <v>0.0466</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.5944</v>
+        <v>0.1631</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.5944</v>
+        <v>-1.3508</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>R. POPA ANDREI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1051</v>
+        <v>-1.8916</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7577</v>
+        <v>-2.4044</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3474</v>
+        <v>0.5128</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6568</v>
+        <v>-2.6426</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2775</v>
+        <v>-0.5341</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9343</v>
+        <v>-2.1085</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1762</v>
+        <v>-1.9626</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7452</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9214</v>
+        <v>-1.4087</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4805</v>
+        <v>-0.68</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4677</v>
+        <v>0.0198</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0129</v>
+        <v>-0.6998</v>
       </c>
       <c r="P21" t="n">
-        <v>0.579</v>
+        <v>0.965</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5441</v>
+        <v>2.8951</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1904</v>
+        <v>-0.9508</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1303</v>
+        <v>-0.9677</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0602</v>
+        <v>0.0168</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1631</v>
+        <v>0.7368</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5138</v>
+        <v>2.4559</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3508</v>
+        <v>-1.7192</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. POPA ANDREI</t>
+          <t>D. MUZQUIZ GURREA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.693</v>
+        <v>-2.297</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.805</v>
+        <v>-1.6279</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1119</v>
+        <v>-0.6691</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6426</v>
+        <v>-2.6178</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5341</v>
+        <v>-1.9717</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.1085</v>
+        <v>-0.6462</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.9626</v>
+        <v>-0.7356</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.7763</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4087</v>
+        <v>0.0407</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.68</v>
+        <v>-1.8822</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0198</v>
+        <v>-1.1953</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6998</v>
+        <v>-0.6869</v>
       </c>
       <c r="P22" t="n">
-        <v>0.965</v>
+        <v>2.5091</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.8951</v>
+        <v>2.5091</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7523</v>
+        <v>-0.5939</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3682</v>
+        <v>-0.8923</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3841</v>
+        <v>0.2984</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7368</v>
+        <v>-1.5944</v>
       </c>
       <c r="W22" t="n">
-        <v>2.4559</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7192</v>
+        <v>-1.5944</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0643</v>
+        <v>-2.9037</v>
       </c>
       <c r="E23" t="n">
         <v>-2.4043</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6601</v>
+        <v>-0.4995</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7131</v>
@@ -2248,13 +2248,13 @@
         <v>1.7371</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7548</v>
+        <v>-0.5942</v>
       </c>
       <c r="T23" t="n">
         <v>-0.5949</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.16</v>
+        <v>0.0007</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3684</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3654</v>
+        <v>-3.0184</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4034</v>
+        <v>-1.0029</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.962</v>
+        <v>-2.0155</v>
       </c>
       <c r="G24" t="n">
         <v>-1.1472</v>
@@ -2326,13 +2326,13 @@
         <v>1.5441</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8672</v>
+        <v>-0.5202</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8923</v>
+        <v>-0.4918</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0251</v>
+        <v>-0.0284</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.3892</v>
+        <v>-6.8015</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.7735</v>
+        <v>-5.373</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6156</v>
+        <v>-1.4286</v>
       </c>
       <c r="G25" t="n">
         <v>-6.0031</v>
@@ -2404,13 +2404,13 @@
         <v>2.7021</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1528</v>
+        <v>-0.5651</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9518</v>
+        <v>-0.5512</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.201</v>
+        <v>-0.0139</v>
       </c>
       <c r="V25" t="n">
         <v>-0.0403</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.0648</v>
+        <v>-16.7296</v>
       </c>
       <c r="E26" t="n">
         <v>-12.9764</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.0884</v>
+        <v>-3.7533</v>
       </c>
       <c r="G26" t="n">
         <v>-18.5882</v>
@@ -2470,7 +2470,7 @@
         <v>-8.9826</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.233500000000001</v>
+        <v>-6.233499999999999</v>
       </c>
       <c r="P26" t="n">
         <v>6.755300000000001</v>
@@ -2482,13 +2482,13 @@
         <v>20.2659</v>
       </c>
       <c r="S26" t="n">
-        <v>-7.8723</v>
+        <v>-6.5371</v>
       </c>
       <c r="T26" t="n">
-        <v>-6.774899999999999</v>
+        <v>-6.775</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.0977</v>
+        <v>0.2378</v>
       </c>
       <c r="V26" t="n">
         <v>1.6406</v>
